--- a/origin-step-json-availability.xlsx
+++ b/origin-step-json-availability.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Origin Step JSON'!$A$1:$G$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Origin Step JSON'!$A$1:$G$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,16 +536,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -714,7 +714,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_4HDU.json</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_CCU.json</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_5HDU.json</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_5HDU.json</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_CCU.json</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_5HDU.json</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_5ICU.json</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_4ICU.json</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_5ICU.json</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_5ICU.json</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_5OT.json</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_5OT.json</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_5OT.json</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_7OT.json</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_4ICU.json</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_4ICU.json</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_4ICU.json</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_5ICU.json</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_3OT.json</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_5OT.json</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_3OT.json</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_7OT.json</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_Private.json</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_South.json</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_Burns.json</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_South.json</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_CIC.json</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_critical.json</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_CIC.json</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCBTC_EMW.json</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - Transfer_00_South.json</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2184,27 +2184,27 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - MCB_IPEB_AED.json</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A - direct route</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A - direct route</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A - direct route</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A - direct route</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_SCBU.json</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_NICU.json</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_SCBU.json</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_O&amp;G_PRI.json</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - IPEB_L&amp;D.json</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>5F . 5/F . EF . 5F Gynaecology Ward</t>
+          <t>6EF . 6/F . EF . 6EF Delivery Suite</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Yes - EF_F.json</t>
+          <t>Yes - EF_E.json</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Yes - EF_South.json</t>
+          <t>Yes - EF_North.json</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Yes - IPEB_A.json</t>
+          <t>Yes - IPEB_L&amp;D.json</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>A16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>C16 . 16/F . IPEB . Labour &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -3684,17 +3684,54 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
+          <t>Yes - IPEB_A.json</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>A16 . 16/F . IPEB . O&amp;G Ward</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>5F . 5/F . EF . 5F Gynaecology Ward</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Yes - EF_F.json</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Yes - EF_South.json</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>Yes - IPEB_B.json</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>B16 . 16/F . IPEB . O&amp;G Ward</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G85"/>
+  <autoFilter ref="A1:G86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3706,11 +3743,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3728,96 +3765,60 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source of origin/destination rows</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Current route-directory.json after hidden-origin filtering</t>
+          <t>Current route-directory plus current index.html auto-match rules</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Step 1 matching</t>
+          <t>Origin filtering</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>By origin route / block JSON</t>
+          <t>Uses the app hidden-origin filter, so hidden origins stay excluded</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Step 2 matching</t>
+          <t>Step 2 / Step 4</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No bundled step JSON configured</t>
+          <t>No JSON auto-match; shown as No unless direct AED route</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Step 3 matching</t>
+          <t>AED route</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>By origin routeKey plus north/south lobby selection</t>
+          <t>MCBTC A&amp;E to IPEB A&amp;E is a direct one-step route; Step 2-5 show N/A - direct route</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Step 4 matching</t>
+          <t>Generated rows</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No bundled step JSON configured</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Step 5 matching</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>By IPEB destination wing JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Current Step 5 coverage</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>IPEB A and IPEB B only; IPEB C/D currently return No</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>MCBTC Step 3 coverage</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>South only; north currently returns No</t>
+          <t>85</t>
         </is>
       </c>
     </row>

--- a/origin-step-json-availability.xlsx
+++ b/origin-step-json-availability.xlsx
@@ -539,13 +539,13 @@
   <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -618,7 +618,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>B11 . 11/F . IPEB . NIV/GI Ward</t>
+          <t>B11 IPEB . NIV/GI Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>C11 . 11/F . IPEB . M&amp;T Dept Office</t>
+          <t>M&amp;T Dept Office . 11/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>B14 . 14/F . IPEB . Medical Ward</t>
+          <t>B14 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>D4 . 4/F . IPEB . HDU (4/F)</t>
+          <t>HDU (4/F) . 4/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>B10 . 10/F . IPEB . CTS Ward</t>
+          <t>B10 IPEB . CTS Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>C10 . 10/F . IPEB . CCU</t>
+          <t>CCU . 10/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>D5 . 5/F . IPEB . HDU (5/F)</t>
+          <t>HDU (5/F) . 5/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>B8 . 8/F . IPEB . Surgical Ward</t>
+          <t>B8 IPEB . Surgical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>A11 . 11/F . IPEB . GI Ward</t>
+          <t>A11 IPEB . GI Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>D5 . 5/F . IPEB . HDU (5/F)</t>
+          <t>HDU (5/F) . 5/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>A10 . 10/F . IPEB . CTS Ward</t>
+          <t>A10 IPEB . CTS Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>C10 . 10/F . IPEB . CCU</t>
+          <t>CCU . 10/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>B11 . 11/F . IPEB . NIV/GI Ward</t>
+          <t>B11 IPEB . NIV/GI Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>B19 . 19/F . IPEB . ISOL Ward B</t>
+          <t>B19 IPEB . ISOL Ward B . IPEB</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>A13 . 13/F . IPEB . MSK Ward A</t>
+          <t>A13 IPEB . MSK Ward A . IPEB</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>B13 . 13/F . IPEB . MSK Ward B</t>
+          <t>B13 IPEB . MSK Ward B . IPEB</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>A13 . 13/F . IPEB . MSK Ward A</t>
+          <t>A13 IPEB . MSK Ward A . IPEB</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>B13 . 13/F . IPEB . MSK Ward B</t>
+          <t>B13 IPEB . MSK Ward B . IPEB</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>A13 . 13/F . IPEB . MSK Ward A</t>
+          <t>A13 IPEB . MSK Ward A . IPEB</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>B13 . 13/F . IPEB . MSK Ward B</t>
+          <t>B13 IPEB . MSK Ward B . IPEB</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>D5 . 5/F . IPEB . HDU (5/F)</t>
+          <t>HDU (5/F) . 5/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -1395,14 +1395,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A9 . 9/F . IPEB . NEURO Ward</t>
+          <t>A9 IPEB . NEURO Ward . IPEB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>5D . 5/F . MCBTC . ICU (5/F)</t>
+          <t>ICU (5/F) . 5/F . MCBTC</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1432,14 +1432,14 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>D4 . 4/F . IPEB . ICU (4/F)</t>
+          <t>ICU (4/F) . 4/F . IPEB</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>5D . 5/F . MCBTC . ICU (5/F)</t>
+          <t>ICU (5/F) . 5/F . MCBTC</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1469,14 +1469,14 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>D5 . 5/F . IPEB . ICU (5/F)</t>
+          <t>ICU (5/F) . 5/F . IPEB</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>5D . 5/F . MCBTC . OT (5/F)</t>
+          <t>OT (5/F) . 5/F . MCBTC</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1506,14 +1506,14 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>D5 . 5/F . IPEB . Peri-op Suite 1</t>
+          <t>Peri-op Suite 1 . 5/F . IPEB</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>5D . 5/F . MCBTC . OT (5/F)</t>
+          <t>OT (5/F) . 5/F . MCBTC</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1543,14 +1543,14 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>D7 . 7/F . IPEB . Peri-op Suite 2</t>
+          <t>Peri-op Suite 2 . 7/F . IPEB</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>4D . 4/F . MCBTC . ICU (4/F)</t>
+          <t>ICU (4/F) . 4/F . MCBTC</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1580,14 +1580,14 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>D4 . 4/F . IPEB . ICU (4/F)</t>
+          <t>ICU (4/F) . 4/F . IPEB</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>4D . 4/F . MCBTC . ICU (4/F)</t>
+          <t>ICU (4/F) . 4/F . MCBTC</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>D5 . 5/F . IPEB . ICU (5/F)</t>
+          <t>ICU (5/F) . 5/F . IPEB</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>3D . 3/F . MCBTC . OT (3/F)</t>
+          <t>OT (3/F) . 3/F . MCBTC</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>D5 . 5/F . IPEB . Peri-op Suite 1</t>
+          <t>Peri-op Suite 1 . 5/F . IPEB</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>3D . 3/F . MCBTC . OT (3/F)</t>
+          <t>OT (3/F) . 3/F . MCBTC</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>D7 . 7/F . IPEB . Peri-op Suite 2</t>
+          <t>Peri-op Suite 2 . 7/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>B10 . 10/F . IPEB . CTS Ward</t>
+          <t>B10 IPEB . CTS Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>A19 . 19/F . IPEB . ISOL Ward A</t>
+          <t>A19 IPEB . ISOL Ward A . IPEB</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>B15 . 15/F . IPEB . Medical Ward</t>
+          <t>B15 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>A15 . 15/F . IPEB . Medical Ward</t>
+          <t>A15 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A9 . 9/F . IPEB . NEURO Ward</t>
+          <t>A9 IPEB . NEURO Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>B12 . 12/F . IPEB . RENAL/URO Ward</t>
+          <t>B12 IPEB . RENAL/URO Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>B8 . 8/F . IPEB . Surgical Ward</t>
+          <t>B8 IPEB . Surgical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>A11 . 11/F . IPEB . GI Ward</t>
+          <t>A11 IPEB . GI Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2024,14 +2024,14 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>B9 . 9/F . IPEB . NEURO Ward</t>
+          <t>B9 IPEB . NEURO Ward . IPEB</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>6D . 6/F . MCBTC . Private Ward</t>
+          <t>Private Ward . 6/F . MCBTC</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2061,14 +2061,14 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>B18 . 18/F . IPEB . PAED IP Ward</t>
+          <t>B18 IPEB . PAED IP Ward . IPEB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>5D . 5/F . MCBTC . Burns Centre</t>
+          <t>Burns Centre . 5/F . MCBTC</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>A10 . 10/F . IPEB . CTS Ward</t>
+          <t>A10 IPEB . CTS Ward . IPEB</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2D . 2/F . MCBTC . Cardiovascular Intervention Centre</t>
+          <t>Cardiovascular Intervention Centre . 2/F . MCBTC</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2135,14 +2135,14 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>C10 . 10/F . IPEB . CIC</t>
+          <t>CIC . 10/F . IPEB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2D . 2/F . MCBTC . EM Ward</t>
+          <t>EM Ward . 2/F . MCBTC</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>A8 . 8/F . IPEB . EM Ward</t>
+          <t>A8 IPEB . EM Ward . IPEB</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>0D . 0/F . MCBTC . A&amp;E</t>
+          <t>A&amp;E . 0/F . MCBTC</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>D0 . 0/F . IPEB . A&amp;E</t>
+          <t>A&amp;E . 0/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>B18 . 18/F . IPEB . PAED IP Ward</t>
+          <t>B18 IPEB . PAED IP Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>A17 . 17/F . IPEB . PAED ISOL Ward</t>
+          <t>A17 IPEB . PAED ISOL Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>A17 . 17/F . IPEB . PAED ISOL Ward</t>
+          <t>A17 IPEB . PAED ISOL Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>A12 . 12/F . IPEB . Medical Ward</t>
+          <t>A12 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>A12 . 12/F . IPEB . Medical Ward</t>
+          <t>A12 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>A14 . 14/F . IPEB . Medical Ward</t>
+          <t>A14 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>B14 . 14/F . IPEB . Medical Ward</t>
+          <t>B14 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>A14 . 14/F . IPEB . Medical Ward</t>
+          <t>A14 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>B14 . 14/F . IPEB . Medical Ward</t>
+          <t>B14 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>A14 . 14/F . IPEB . Medical Ward</t>
+          <t>A14 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>B14 . 14/F . IPEB . Medical Ward</t>
+          <t>B14 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>B8 . 8/F . IPEB . Surgical Ward</t>
+          <t>B8 IPEB . Surgical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>A11 . 11/F . IPEB . GI Ward</t>
+          <t>A11 IPEB . GI Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>B12 . 12/F . IPEB . RENAL/URO Ward</t>
+          <t>B12 IPEB . RENAL/URO Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>B8 . 8/F . IPEB . Surgical Ward</t>
+          <t>B8 IPEB . Surgical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>A11 . 11/F . IPEB . GI Ward</t>
+          <t>A11 IPEB . GI Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>B12 . 12/F . IPEB . RENAL/URO Ward</t>
+          <t>B12 IPEB . RENAL/URO Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>A18 . 18/F . IPEB . PAED SUR/ORT Ward</t>
+          <t>A18 IPEB . PAED SUR/ORT Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>A18 . 18/F . IPEB . PAED SUR/ORT Ward</t>
+          <t>A18 IPEB . PAED SUR/ORT Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>C17 . 17/F . IPEB . SCBU</t>
+          <t>SCBU . 17/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>C17 . 17/F . IPEB . NICU</t>
+          <t>NICU . 17/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>C17 . 17/F . IPEB . SCBU</t>
+          <t>SCBU . 17/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>B17 . 17/F . IPEB . PICU</t>
+          <t>B17 IPEB . PICU . IPEB</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>B11 . 11/F . IPEB . NIV/GI Ward</t>
+          <t>B11 IPEB . NIV/GI Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>A15 . 15/F . IPEB . Medical Ward</t>
+          <t>A15 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>B15 . 15/F . IPEB . Medical Ward</t>
+          <t>B15 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>B11 . 11/F . IPEB . NIV/GI Ward</t>
+          <t>B11 IPEB . NIV/GI Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>A15 . 15/F . IPEB . Medical Ward</t>
+          <t>A15 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>B15 . 15/F . IPEB . Medical Ward</t>
+          <t>B15 IPEB . Medical Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>C15 . 15/F . IPEB . O&amp;G Private</t>
+          <t>O&amp;G Private . 15/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>A16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>A16 IPEB . O&amp;G Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>B16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>B16 IPEB . O&amp;G Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>A16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>A16 IPEB . O&amp;G Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>B16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>B16 IPEB . O&amp;G Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>C16 . 16/F . IPEB . Integrated Birth</t>
+          <t>Integrated Birth . 16/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>A16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>A16 IPEB . O&amp;G Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>B16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>B16 IPEB . O&amp;G Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>C16 . 16/F . IPEB . Labour &amp; Delivery</t>
+          <t>Labour &amp; Delivery . 16/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>C16 . 16/F . IPEB . Labour &amp; Delivery</t>
+          <t>Labour &amp; Delivery . 16/F . IPEB</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>A16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>A16 IPEB . O&amp;G Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>B16 . 16/F . IPEB . O&amp;G Ward</t>
+          <t>B16 IPEB . O&amp;G Ward . IPEB</t>
         </is>
       </c>
     </row>
@@ -3743,10 +3743,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -3765,58 +3765,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Final destination A/B format</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Current route-directory plus current index.html auto-match rules</t>
+          <t>wardCode + building, then area, then building again, following your latest example</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Origin filtering</t>
+          <t>Final destination C/D format</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Uses the app hidden-origin filter, so hidden origins stay excluded</t>
+          <t>area first, then floor, then building</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Step 2 / Step 4</t>
+          <t>Origin D format</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No JSON auto-match; shown as No unless direct AED route</t>
+          <t>area first, then floor, then building</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AED route</t>
+          <t>Generated rows</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MCBTC A&amp;E to IPEB A&amp;E is a direct one-step route; Step 2-5 show N/A - direct route</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Generated rows</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
